--- a/artifacts/output/test7_output.xlsx
+++ b/artifacts/output/test7_output.xlsx
@@ -419,41 +419,53 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Coefficient</t>
+          <t>Weight</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Temperature (F)</t>
-        </is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-32.08127157209802</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ice-cream Price ($)</t>
-        </is>
+          <t>Temperature (F)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.6010053253314011</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Number of Tourists (thousands)</t>
-        </is>
+          <t>Ice-cream Price ($)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.362298890765464</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ice Cream Sales ($,thousands)</t>
-        </is>
+          <t>Number of Tourists (thousands)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.7994885680697196</v>
       </c>
     </row>
   </sheetData>
